--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-blueberry_tiny_3.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-blueberry_tiny_3.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>49.69220423698425</v>
+        <v>57.07995390892029</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>15.43000030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>0.144377107421557</v>
+        <v>0.4704527681072553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9066666960716248</v>
+        <v>0.8732394576072693</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7840405106544495</v>
+        <v>0.8167939186096191</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7832699418067932</v>
+        <v>0.809271514415741</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7860317230224609</v>
+        <v>0.8084824681282043</v>
       </c>
       <c r="J2" t="n">
-        <v>0.111276589334011</v>
+        <v>0.1859183460474014</v>
       </c>
       <c r="K2" t="n">
-        <v>19.14726209640503</v>
+        <v>58.54171085357666</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06345190048217771</v>
+        <v>0.1100143146514892</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1244076299667358</v>
+        <v>0.5015810680389404</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1255463933944702</v>
+        <v>0.21201500415802</v>
       </c>
       <c r="O2" t="n">
-        <v>3.172595024108887</v>
+        <v>5.500715732574463</v>
       </c>
       <c r="P2" t="n">
-        <v>6.220381498336792</v>
+        <v>25.07905340194702</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.277319669723511</v>
+        <v>10.600750207901</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-161301</t>
+          <t>20250725-225621</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -720,53 +720,53 @@
         <v>34</v>
       </c>
       <c r="C3" t="n">
-        <v>31.62995886802673</v>
+        <v>76.7237753868103</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5</v>
+        <v>15.43000030517578</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1449878141283988</v>
+        <v>0.4717928688315784</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8799999952316284</v>
+        <v>0.9166666865348816</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7586206793785095</v>
+        <v>0.7989854216575623</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7161383032798767</v>
+        <v>0.792225182056427</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7181687951087952</v>
+        <v>0.7904509305953979</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1112867817282676</v>
+        <v>0.180614948272705</v>
       </c>
       <c r="K3" t="n">
-        <v>19.35022640228271</v>
+        <v>63.44678473472595</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0563068914413452</v>
+        <v>0.1118973016738891</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1168089866638183</v>
+        <v>0.5040094327926635</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1200147533416748</v>
+        <v>0.2153144550323486</v>
       </c>
       <c r="O3" t="n">
-        <v>2.815344572067261</v>
+        <v>5.594865083694458</v>
       </c>
       <c r="P3" t="n">
-        <v>5.840449333190918</v>
+        <v>25.20047163963318</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.00073766708374</v>
+        <v>10.76572275161743</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-161505</t>
+          <t>20250725-225947</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,56 +838,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>58.61772918701172</v>
+        <v>66.27030324935913</v>
       </c>
       <c r="D4" t="n">
-        <v>6.519999980926514</v>
+        <v>15.43000030517578</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1470048248302191</v>
+        <v>0.4709871370216896</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9142857193946838</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7830065488815308</v>
+        <v>0.7605969905853271</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7368420958518982</v>
+        <v>0.760855495929718</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7357811331748962</v>
+        <v>0.7561290264129639</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1075381636619567</v>
+        <v>0.1783635765314102</v>
       </c>
       <c r="K4" t="n">
-        <v>19.63300824165344</v>
+        <v>62.3372757434845</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0698004245758056</v>
+        <v>0.09932807922363281</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1145829391479492</v>
+        <v>0.4990205287933349</v>
       </c>
       <c r="N4" t="n">
-        <v>0.122821397781372</v>
+        <v>0.2099088096618652</v>
       </c>
       <c r="O4" t="n">
-        <v>3.490021228790283</v>
+        <v>4.966403961181641</v>
       </c>
       <c r="P4" t="n">
-        <v>5.729146957397461</v>
+        <v>24.95102643966675</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.141069889068604</v>
+        <v>10.49544048309326</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-161650</t>
+          <t>20250725-230338</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>31.59505128860474</v>
+        <v>66.96689081192017</v>
       </c>
       <c r="D5" t="n">
-        <v>6.5</v>
+        <v>15.43000030517578</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1449846388662562</v>
+        <v>0.4700256586074829</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8767123222351074</v>
+        <v>0.8857142925262451</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7618412375450134</v>
+        <v>0.8247810006141663</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7045454382896423</v>
+        <v>0.8111332058906555</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7080181837081909</v>
+        <v>0.802395224571228</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1134355962276458</v>
+        <v>0.1839371174573898</v>
       </c>
       <c r="K5" t="n">
-        <v>19.16315317153931</v>
+        <v>63.23137474060059</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0587211656570434</v>
+        <v>0.1089053201675415</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1153432512283325</v>
+        <v>0.5055176830291748</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1324038314819336</v>
+        <v>0.2113512420654296</v>
       </c>
       <c r="O5" t="n">
-        <v>2.936058282852173</v>
+        <v>5.445266008377075</v>
       </c>
       <c r="P5" t="n">
-        <v>5.767162561416626</v>
+        <v>25.27588415145874</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.62019157409668</v>
+        <v>10.56756210327148</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-161903</t>
+          <t>20250725-230717</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>45.83732128143311</v>
+        <v>76.83988189697266</v>
       </c>
       <c r="D6" t="n">
-        <v>6.5</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1459119140493626</v>
+        <v>0.4703031839693294</v>
       </c>
       <c r="F6" t="n">
-        <v>0.931506872177124</v>
+        <v>0.9350649118423462</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8071519732475281</v>
+        <v>0.8073047995567322</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8057366609573364</v>
+        <v>0.803118884563446</v>
       </c>
       <c r="I6" t="n">
-        <v>0.802890956401825</v>
+        <v>0.7982004880905151</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1165434867143631</v>
+        <v>0.1809172481298446</v>
       </c>
       <c r="K6" t="n">
-        <v>19.15483283996582</v>
+        <v>68.36982560157776</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0696837377548217</v>
+        <v>0.1207693576812744</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1237140655517578</v>
+        <v>0.5063634729385376</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1333547258377075</v>
+        <v>0.2171226692199707</v>
       </c>
       <c r="O6" t="n">
-        <v>3.484186887741089</v>
+        <v>6.038467884063721</v>
       </c>
       <c r="P6" t="n">
-        <v>6.185703277587891</v>
+        <v>25.31817364692688</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.667736291885376</v>
+        <v>10.85613346099854</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-162049</t>
+          <t>20250725-231057</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C2" t="n">
-        <v>96.30785655975342</v>
+        <v>539.3624341487885</v>
       </c>
       <c r="D2" t="n">
-        <v>9.829999923706056</v>
+        <v>20.56999969482422</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2905236775124514</v>
+        <v>0.543818510549013</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9041095972061156</v>
+        <v>0.9333333373069764</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8147239089012146</v>
+        <v>0.792682945728302</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8159509301185608</v>
+        <v>0.7368420958518982</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8142589330673218</v>
+        <v>0.09655172377824781</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1305057853460312</v>
+        <v>0.158623918890953</v>
       </c>
       <c r="K2" t="n">
-        <v>80.62542939186096</v>
+        <v>75.83283543586731</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1084847831726074</v>
+        <v>0.1122391271591186</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5058449125289917</v>
+        <v>0.2421033811569214</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2091801977157592</v>
+        <v>0.2354425144195556</v>
       </c>
       <c r="O2" t="n">
-        <v>5.424239158630371</v>
+        <v>5.611956357955933</v>
       </c>
       <c r="P2" t="n">
-        <v>25.29224562644958</v>
+        <v>12.10516905784607</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.45900988578796</v>
+        <v>11.77212572097778</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-062504</t>
+          <t>20250724-161853</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="C3" t="n">
-        <v>59.6267294883728</v>
+        <v>391.9788656234741</v>
       </c>
       <c r="D3" t="n">
-        <v>9.739999771118164</v>
+        <v>20.54000091552734</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2884821199318942</v>
+        <v>0.5252724108286202</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8918918967247009</v>
+        <v>0.9610389471054076</v>
       </c>
       <c r="G3" t="n">
-        <v>0.807894766330719</v>
+        <v>0.8070841431617737</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8105263113975525</v>
+        <v>0.7222222089767456</v>
       </c>
       <c r="I3" t="n">
-        <v>0.805793285369873</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1309553682804107</v>
+        <v>0.1676723361015319</v>
       </c>
       <c r="K3" t="n">
-        <v>75.00895476341248</v>
+        <v>82.21448016166687</v>
       </c>
       <c r="L3" t="n">
-        <v>0.121320776939392</v>
+        <v>0.1167242574691772</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5078200006484985</v>
+        <v>0.2455184698104858</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2192995500564575</v>
+        <v>0.2260103034973144</v>
       </c>
       <c r="O3" t="n">
-        <v>6.066038846969604</v>
+        <v>5.836212873458862</v>
       </c>
       <c r="P3" t="n">
-        <v>25.39100003242493</v>
+        <v>12.27592349052429</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.96497750282288</v>
+        <v>11.30051517486572</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-062933</t>
+          <t>20250724-163040</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C4" t="n">
-        <v>44.02047610282898</v>
+        <v>462.6263689994812</v>
       </c>
       <c r="D4" t="n">
-        <v>9.779999732971191</v>
+        <v>21.09000015258789</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2898744394381841</v>
+        <v>0.5261688284777306</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8684210777282715</v>
+        <v>0.9473684430122375</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7936117649078369</v>
+        <v>0.8448687195777893</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7351190447807312</v>
+        <v>0.8307493329048157</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7268656492233276</v>
+        <v>0.8282566666603088</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1317107081413269</v>
+        <v>0.1591765284538269</v>
       </c>
       <c r="K4" t="n">
-        <v>86.51803660392761</v>
+        <v>82.69192624092102</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1022862291336059</v>
+        <v>0.1178730106353759</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4990139436721801</v>
+        <v>0.24715341091156</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2074529075622558</v>
+        <v>0.2444097280502319</v>
       </c>
       <c r="O4" t="n">
-        <v>5.114311456680298</v>
+        <v>5.893650531768799</v>
       </c>
       <c r="P4" t="n">
-        <v>24.95069718360901</v>
+        <v>12.357670545578</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.37264537811279</v>
+        <v>12.2204864025116</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-063321</t>
+          <t>20250724-164009</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>52.1279764175415</v>
+        <v>421.9297790527344</v>
       </c>
       <c r="D5" t="n">
-        <v>9.810000419616699</v>
+        <v>19.40999984741211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2873089354613731</v>
+        <v>0.551957805087601</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8857142925262451</v>
+        <v>0.9333333373069764</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8142589330673218</v>
+        <v>0.7759361863136292</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7928176522254944</v>
+        <v>0.7426573634147644</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7864077687263489</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1269367486238479</v>
+        <v>0.1632633656263351</v>
       </c>
       <c r="K5" t="n">
-        <v>85.26201558113098</v>
+        <v>82.26832294464111</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1129649019241333</v>
+        <v>0.1303762626647949</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5063089275360108</v>
+        <v>0.2467827177047729</v>
       </c>
       <c r="N5" t="n">
-        <v>0.212115249633789</v>
+        <v>0.2326191186904907</v>
       </c>
       <c r="O5" t="n">
-        <v>5.648245096206665</v>
+        <v>6.518813133239746</v>
       </c>
       <c r="P5" t="n">
-        <v>25.31544637680054</v>
+        <v>12.33913588523865</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.60576248168945</v>
+        <v>11.63095593452454</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-063703</t>
+          <t>20250724-165052</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C6" t="n">
-        <v>44.16688704490662</v>
+        <v>417.3235845565796</v>
       </c>
       <c r="D6" t="n">
-        <v>9.779999732971191</v>
+        <v>20.8799991607666</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2901690465708573</v>
+        <v>0.5376854141553243</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9066666960716248</v>
+        <v>0.7945205569267273</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8185185194015503</v>
+        <v>0.6290322542190552</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7716092467308044</v>
+        <v>0.6222808361053467</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7620396614074707</v>
+        <v>0.6286836862564087</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1323260366916656</v>
+        <v>0.164865031838417</v>
       </c>
       <c r="K6" t="n">
-        <v>82.2913703918457</v>
+        <v>75.26547122001648</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1100447416305542</v>
+        <v>0.1260698413848877</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4993826913833618</v>
+        <v>0.2528633069992065</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2087044382095337</v>
+        <v>0.2403993654251098</v>
       </c>
       <c r="O6" t="n">
-        <v>5.50223708152771</v>
+        <v>6.303492069244385</v>
       </c>
       <c r="P6" t="n">
-        <v>24.96913456916809</v>
+        <v>12.64316534996033</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.43522191047668</v>
+        <v>12.01996827125549</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-064053</t>
+          <t>20250724-170041</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C2" t="n">
-        <v>393.4135863780975</v>
+        <v>367.2725667953491</v>
       </c>
       <c r="D2" t="n">
-        <v>14.1899995803833</v>
+        <v>9.989999771118164</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4865667251440195</v>
+        <v>0.4627678687455224</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8732394576072693</v>
+        <v>0.931506872177124</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8211179971694946</v>
+        <v>0.7738693356513977</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7541697025299072</v>
+        <v>0.7203450798988342</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.7045952081680298</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1506150960922241</v>
+        <v>0.1738146543502807</v>
       </c>
       <c r="K2" t="n">
-        <v>82.11574792861938</v>
+        <v>74.26253890991211</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1174254560470581</v>
+        <v>0.1214058637619018</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2472856712341308</v>
+        <v>0.2825319910049438</v>
       </c>
       <c r="N2" t="n">
-        <v>0.232066855430603</v>
+        <v>0.2229264736175537</v>
       </c>
       <c r="O2" t="n">
-        <v>5.871272802352905</v>
+        <v>6.070293188095093</v>
       </c>
       <c r="P2" t="n">
-        <v>12.36428356170654</v>
+        <v>14.12659955024719</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.60334277153015</v>
+        <v>11.14632368087769</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-131352</t>
+          <t>20250727-013452</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C3" t="n">
-        <v>355.5179376602173</v>
+        <v>427.4442319869995</v>
       </c>
       <c r="D3" t="n">
-        <v>14.51000022888184</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4673057804673405</v>
+        <v>0.4641952416614482</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9189189076423644</v>
+        <v>0.9473684430122375</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8308065533638</v>
+        <v>0.8438060879707336</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8169381022453308</v>
+        <v>0.8054053783416748</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8111615777015686</v>
+        <v>0.814063549041748</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1582341492176056</v>
+        <v>0.1723667979240417</v>
       </c>
       <c r="K3" t="n">
-        <v>82.0108745098114</v>
+        <v>67.10034799575806</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1308561754226684</v>
+        <v>0.1254089498519897</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2444526958465576</v>
+        <v>0.2674295806884765</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2424906682968139</v>
+        <v>0.2184987831115722</v>
       </c>
       <c r="O3" t="n">
-        <v>6.542808771133423</v>
+        <v>6.270447492599487</v>
       </c>
       <c r="P3" t="n">
-        <v>12.22263479232788</v>
+        <v>13.37147903442383</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.1245334148407</v>
+        <v>10.92493915557861</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-132313</t>
+          <t>20250727-014347</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>384.4054915904999</v>
+        <v>338.3554232120514</v>
       </c>
       <c r="D4" t="n">
-        <v>14.27999973297119</v>
+        <v>10.22000026702881</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4746402639609117</v>
+        <v>0.4474701111922499</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9166666865348816</v>
+        <v>0.7397260069847107</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8045427203178406</v>
+        <v>0.4974396526813507</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7684729099273682</v>
+        <v>0.4831130802631378</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.1749460101127624</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1533432006835937</v>
+        <v>0.1624983847141266</v>
       </c>
       <c r="K4" t="n">
-        <v>76.10964322090149</v>
+        <v>70.32452130317688</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1254559183120727</v>
+        <v>0.1137797737121582</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2429945278167724</v>
+        <v>0.2636447811126709</v>
       </c>
       <c r="N4" t="n">
-        <v>0.220391936302185</v>
+        <v>0.2149000883102417</v>
       </c>
       <c r="O4" t="n">
-        <v>6.272795915603638</v>
+        <v>5.68898868560791</v>
       </c>
       <c r="P4" t="n">
-        <v>12.14972639083862</v>
+        <v>13.18223905563354</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.01959681510925</v>
+        <v>10.74500441551208</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-133208</t>
+          <t>20250727-015341</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
-        <v>372.7273499965668</v>
+        <v>260.4235870838165</v>
       </c>
       <c r="D5" t="n">
-        <v>14.4399995803833</v>
+        <v>9.710000038146973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4842258874447115</v>
+        <v>0.4958499629389156</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9113923907279968</v>
+        <v>0.6829268336296082</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8253012299537659</v>
+        <v>0.5423497557640076</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7422382831573486</v>
+        <v>0.5258493423461914</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7445573210716248</v>
+        <v>0.0645161271095275</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1584929525852203</v>
+        <v>0.1686611920595169</v>
       </c>
       <c r="K5" t="n">
-        <v>76.0516893863678</v>
+        <v>74.00279021263123</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1156018733978271</v>
+        <v>0.1132704353332519</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2392068672180175</v>
+        <v>0.2702524042129516</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2314082908630371</v>
+        <v>0.2018306303024292</v>
       </c>
       <c r="O5" t="n">
-        <v>5.780093669891357</v>
+        <v>5.663521766662598</v>
       </c>
       <c r="P5" t="n">
-        <v>11.96034336090088</v>
+        <v>13.51262021064758</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.57041454315186</v>
+        <v>10.09153151512146</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-134131</t>
+          <t>20250727-020151</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>372.946989774704</v>
+        <v>320.2023746967316</v>
       </c>
       <c r="D6" t="n">
-        <v>14.46000003814697</v>
+        <v>10.06999969482422</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4787767802254628</v>
+        <v>0.4816422917932834</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9166666865348816</v>
+        <v>0.9333333373069764</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8114144206047058</v>
+        <v>0.8392204642295837</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7746288776397705</v>
+        <v>0.8296390175819397</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7670300006866455</v>
+        <v>0.0492957755923271</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1565674245357513</v>
+        <v>0.1757715791463852</v>
       </c>
       <c r="K6" t="n">
-        <v>81.62076544761658</v>
+        <v>68.45891237258911</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1267878866195678</v>
+        <v>0.1172003936767578</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2416765975952148</v>
+        <v>0.2748340797424316</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2342291212081909</v>
+        <v>0.2166563415527344</v>
       </c>
       <c r="O6" t="n">
-        <v>6.339394330978394</v>
+        <v>5.860019683837891</v>
       </c>
       <c r="P6" t="n">
-        <v>12.08382987976074</v>
+        <v>13.74170398712158</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.71145606040955</v>
+        <v>10.83281707763672</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-135041</t>
+          <t>20250727-020857</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>270.7546472549438</v>
+        <v>191.9597165584564</v>
       </c>
       <c r="D2" t="n">
-        <v>9.420000076293944</v>
+        <v>5.519999980926514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4310023387273152</v>
+        <v>0.2965299114584923</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9014084339141846</v>
+        <v>0.7714285850524902</v>
       </c>
       <c r="G2" t="n">
-        <v>0.756594717502594</v>
+        <v>0.6666666865348816</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7248968482017517</v>
+        <v>0.6300783753395081</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6686522960662842</v>
+        <v>0.6307471394538879</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1687303781509399</v>
+        <v>0.1465024501085281</v>
       </c>
       <c r="K2" t="n">
-        <v>67.92800354957581</v>
+        <v>25.62070989608765</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1296864986419677</v>
+        <v>0.0978364276885986</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2738260269165039</v>
+        <v>0.135204119682312</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2364697456359863</v>
+        <v>0.1482986640930176</v>
       </c>
       <c r="O2" t="n">
-        <v>6.484324932098389</v>
+        <v>4.891821384429932</v>
       </c>
       <c r="P2" t="n">
-        <v>13.6913013458252</v>
+        <v>6.760205984115601</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.82348728179932</v>
+        <v>7.414933204650879</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-025032</t>
+          <t>20250728-052338</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C3" t="n">
-        <v>249.8633053302765</v>
+        <v>178.6031818389893</v>
       </c>
       <c r="D3" t="n">
-        <v>8.930000305175781</v>
+        <v>5.210000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.427273252329161</v>
+        <v>0.3076628057057397</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7848101258277893</v>
+        <v>0.8450704216957092</v>
       </c>
       <c r="G3" t="n">
-        <v>0.691961407661438</v>
+        <v>0.7884984016418457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6785469651222229</v>
+        <v>0.7395451068878174</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3117647171020508</v>
+        <v>0.6776729822158813</v>
       </c>
       <c r="J3" t="n">
-        <v>0.149501085281372</v>
+        <v>0.1411905586719513</v>
       </c>
       <c r="K3" t="n">
-        <v>67.85012340545654</v>
+        <v>19.80722713470459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1336920261383056</v>
+        <v>0.0993399810791015</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2652624702453613</v>
+        <v>0.1273854970932006</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2226424169540405</v>
+        <v>0.1339589118957519</v>
       </c>
       <c r="O3" t="n">
-        <v>6.684601306915283</v>
+        <v>4.966999053955078</v>
       </c>
       <c r="P3" t="n">
-        <v>13.26312351226807</v>
+        <v>6.369274854660034</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.13212084770203</v>
+        <v>6.697945594787598</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-025735</t>
+          <t>20250728-052809</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>275.1835117340088</v>
+        <v>135.7514247894287</v>
       </c>
       <c r="D4" t="n">
-        <v>9.630000114440918</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4651006764553962</v>
+        <v>0.3204123821448196</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8860759735107422</v>
+        <v>0.5432098507881165</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7052023410797119</v>
+        <v>0.3380281627178192</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5953124761581421</v>
+        <v>0.317485898733139</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2415254265069961</v>
+        <v>0.3323529362678528</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1589548140764236</v>
+        <v>0.1433759778738021</v>
       </c>
       <c r="K4" t="n">
-        <v>71.94186305999756</v>
+        <v>25.11080241203308</v>
       </c>
       <c r="L4" t="n">
-        <v>0.125273118019104</v>
+        <v>0.08740536212921141</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2699238538742065</v>
+        <v>0.1190723323822021</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2191435956954956</v>
+        <v>0.1285344791412353</v>
       </c>
       <c r="O4" t="n">
-        <v>6.2636559009552</v>
+        <v>4.370268106460571</v>
       </c>
       <c r="P4" t="n">
-        <v>13.49619269371033</v>
+        <v>5.953616619110107</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.95717978477478</v>
+        <v>6.426723957061768</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-030416</t>
+          <t>20250728-053234</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C5" t="n">
-        <v>278.376585483551</v>
+        <v>199.9030976295471</v>
       </c>
       <c r="D5" t="n">
-        <v>8.859999656677246</v>
+        <v>5.25</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4462727056099818</v>
+        <v>0.3061686863028814</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9090909361839294</v>
+        <v>0.837837815284729</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7678220868110657</v>
+        <v>0.6766541600227356</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7104303240776062</v>
+        <v>0.6636539697647095</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5358931422233582</v>
+        <v>0.6579804420471191</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1545991748571396</v>
+        <v>0.1370179057121276</v>
       </c>
       <c r="K5" t="n">
-        <v>66.48102688789368</v>
+        <v>19.83569669723511</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1333122968673706</v>
+        <v>0.09904712677001951</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2640269327163696</v>
+        <v>0.1259095907211303</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2246301794052124</v>
+        <v>0.1348071956634521</v>
       </c>
       <c r="O5" t="n">
-        <v>6.66561484336853</v>
+        <v>4.952356338500977</v>
       </c>
       <c r="P5" t="n">
-        <v>13.20134663581848</v>
+        <v>6.295479536056519</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.23150897026062</v>
+        <v>6.740359783172607</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-031126</t>
+          <t>20250728-053616</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C6" t="n">
-        <v>256.9826140403748</v>
+        <v>171.6768908500671</v>
       </c>
       <c r="D6" t="n">
-        <v>9.229999542236328</v>
+        <v>5.570000171661377</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4672665090061897</v>
+        <v>0.3175620032982392</v>
       </c>
       <c r="F6" t="n">
-        <v>0.931506872177124</v>
+        <v>0.692307710647583</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7751938104629517</v>
+        <v>0.6315192580223083</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7340350747108459</v>
+        <v>0.6229929327964783</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5883244872093201</v>
+        <v>0.0119904074817895</v>
       </c>
       <c r="J6" t="n">
-        <v>0.147493302822113</v>
+        <v>0.140136569738388</v>
       </c>
       <c r="K6" t="n">
-        <v>61.39963936805725</v>
+        <v>25.22837138175964</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1405206871032714</v>
+        <v>0.0949060678482055</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2642371273040771</v>
+        <v>0.1290427446365356</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2224631118774414</v>
+        <v>0.1224642992019653</v>
       </c>
       <c r="O6" t="n">
-        <v>7.026034355163574</v>
+        <v>4.745303392410278</v>
       </c>
       <c r="P6" t="n">
-        <v>13.21185636520386</v>
+        <v>6.452137231826782</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.12315559387207</v>
+        <v>6.123214960098267</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-031839</t>
+          <t>20250728-054103</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>132.3162512779236</v>
+        <v>212.0192775726318</v>
       </c>
       <c r="D2" t="n">
-        <v>3.140000104904175</v>
+        <v>8.050000190734863</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2943071563576543</v>
+        <v>0.3641800124536861</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7027027010917664</v>
+        <v>0.6944444179534912</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6108312606811523</v>
+        <v>0.5690945982933044</v>
       </c>
       <c r="H2" t="n">
-        <v>0.553892195224762</v>
+        <v>0.5573033690452576</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0048309178091585</v>
+        <v>0.4847972989082336</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1538205295801162</v>
+        <v>0.1659466624259948</v>
       </c>
       <c r="K2" t="n">
-        <v>31.29232239723206</v>
+        <v>39.92482590675354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09798552513122551</v>
+        <v>0.1098107481002807</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1246836137771606</v>
+        <v>0.1883954572677612</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1222529697418212</v>
+        <v>0.1756904745101928</v>
       </c>
       <c r="O2" t="n">
-        <v>4.899276256561279</v>
+        <v>5.490537405014038</v>
       </c>
       <c r="P2" t="n">
-        <v>6.234180688858032</v>
+        <v>9.419772863388062</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.112648487091064</v>
+        <v>8.784523725509644</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-172805</t>
+          <t>20250729-085530</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="C3" t="n">
-        <v>132.2102122306824</v>
+        <v>383.3744971752167</v>
       </c>
       <c r="D3" t="n">
-        <v>3.039999961853028</v>
+        <v>6.659999847412109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3083520782264796</v>
+        <v>0.368687091433272</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.921052634716034</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6022031903266907</v>
+        <v>0.7754585742950439</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6021361947059631</v>
+        <v>0.7807692289352417</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6020593643188477</v>
+        <v>0.6204324960708618</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1488278806209564</v>
+        <v>0.1546110808849334</v>
       </c>
       <c r="K3" t="n">
-        <v>27.5936872959137</v>
+        <v>40.18684720993042</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1023723459243774</v>
+        <v>0.0969928073883056</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1355659484863281</v>
+        <v>0.1924047565460205</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1423668479919433</v>
+        <v>0.1860169553756714</v>
       </c>
       <c r="O3" t="n">
-        <v>5.118617296218872</v>
+        <v>4.849640369415283</v>
       </c>
       <c r="P3" t="n">
-        <v>6.778297424316406</v>
+        <v>9.620237827301024</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.118342399597168</v>
+        <v>9.300847768783569</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-173150</t>
+          <t>20250729-090057</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C4" t="n">
-        <v>136.0691833496094</v>
+        <v>240.6561496257782</v>
       </c>
       <c r="D4" t="n">
-        <v>3.259999990463257</v>
+        <v>7.760000228881836</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3448578486608904</v>
+        <v>0.3835418110092481</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.931506872177124</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6585051417350769</v>
+        <v>0.8321167826652527</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6454734206199646</v>
+        <v>0.8261150717735291</v>
       </c>
       <c r="I4" t="n">
-        <v>0.374072253704071</v>
+        <v>0.8348793983459473</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1460800319910049</v>
+        <v>0.1544452905654907</v>
       </c>
       <c r="K4" t="n">
-        <v>33.77796792984009</v>
+        <v>40.03619813919067</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0965786218643188</v>
+        <v>0.0962291860580444</v>
       </c>
       <c r="M4" t="n">
-        <v>0.122093858718872</v>
+        <v>0.1873467540740966</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1552430009841919</v>
+        <v>0.1885463857650756</v>
       </c>
       <c r="O4" t="n">
-        <v>4.828931093215942</v>
+        <v>4.811459302902222</v>
       </c>
       <c r="P4" t="n">
-        <v>6.104692935943604</v>
+        <v>9.367337703704834</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.762150049209595</v>
+        <v>9.427319288253784</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-173533</t>
+          <t>20250729-090917</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
-        <v>136.8332905769348</v>
+        <v>196.2775852680206</v>
       </c>
       <c r="D5" t="n">
-        <v>2.990000009536743</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3270710540372272</v>
+        <v>0.4101167224023653</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7297297120094299</v>
+        <v>0.8571428656578064</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6252199411392212</v>
+        <v>0.6790582537651062</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6192307472229004</v>
+        <v>0.6755496263504028</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6175528764724731</v>
+        <v>0.3065420687198639</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1437966972589492</v>
+        <v>0.146523892879486</v>
       </c>
       <c r="K5" t="n">
-        <v>26.6987988948822</v>
+        <v>33.77649784088135</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09858613967895501</v>
+        <v>0.104524073600769</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1284275722503662</v>
+        <v>0.192064151763916</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1370229721069336</v>
+        <v>0.1803388166427612</v>
       </c>
       <c r="O5" t="n">
-        <v>4.929306983947754</v>
+        <v>5.226203680038452</v>
       </c>
       <c r="P5" t="n">
-        <v>6.421378612518311</v>
+        <v>9.603207588195801</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.85114860534668</v>
+        <v>9.016940832138062</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-173925</t>
+          <t>20250729-091514</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
-        <v>143.0887150764465</v>
+        <v>281.4397213459015</v>
       </c>
       <c r="D6" t="n">
-        <v>3.059999942779541</v>
+        <v>7.25</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3483006940646605</v>
+        <v>0.3895373515028884</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7297297120094299</v>
+        <v>0.7945205569267273</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6204922795295715</v>
+        <v>0.6885448694229126</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6141538619995117</v>
+        <v>0.6573529243469238</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6200923919677734</v>
+        <v>0.6671575903892517</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1695566177368164</v>
+        <v>0.1437449157238006</v>
       </c>
       <c r="K6" t="n">
-        <v>32.15788555145264</v>
+        <v>40.35482907295227</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1024907493591308</v>
+        <v>0.09872439861297599</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1294346666336059</v>
+        <v>0.1789579916000366</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1428952598571777</v>
+        <v>0.1854653215408325</v>
       </c>
       <c r="O6" t="n">
-        <v>5.124537467956543</v>
+        <v>4.936219930648804</v>
       </c>
       <c r="P6" t="n">
-        <v>6.471733331680298</v>
+        <v>8.947899580001831</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.144762992858887</v>
+        <v>9.273266077041626</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-174311</t>
+          <t>20250729-092021</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>197.5870053768158</v>
+        <v>111.7402472496033</v>
       </c>
       <c r="D2" t="n">
-        <v>7.03000020980835</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.366245298626575</v>
+        <v>0.1384739043435665</v>
       </c>
       <c r="F2" t="n">
-        <v>0.931506872177124</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7482649683952332</v>
+        <v>0.7183787822723389</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7122302055358887</v>
+        <v>0.7144886255264282</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6811492443084717</v>
+        <v>0.7094932198524475</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1613684147596359</v>
+        <v>0.1137841641902923</v>
       </c>
       <c r="K2" t="n">
-        <v>50.74897456169128</v>
+        <v>8.72504186630249</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1056157207489013</v>
+        <v>0.0682408046722412</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1999541759490966</v>
+        <v>0.09375869274139401</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2107506513595581</v>
+        <v>0.09406669616699211</v>
       </c>
       <c r="O2" t="n">
-        <v>5.280786037445068</v>
+        <v>3.412040233612061</v>
       </c>
       <c r="P2" t="n">
-        <v>9.997708797454834</v>
+        <v>4.687934637069702</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.5375325679779</v>
+        <v>4.703334808349609</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-053904</t>
+          <t>20250730-090422</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>182.63818359375</v>
+        <v>118.8642098903656</v>
       </c>
       <c r="D3" t="n">
-        <v>5.96999979019165</v>
+        <v>10.42000007629394</v>
       </c>
       <c r="E3" t="n">
-        <v>0.370243044786675</v>
+        <v>0.137968059342641</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9333333373069764</v>
+        <v>0.8648648858070374</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8201892971992493</v>
+        <v>0.7632461190223694</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8031914830207825</v>
+        <v>0.7599431872367859</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7900403738021851</v>
+        <v>0.758338987827301</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1422280818223953</v>
+        <v>0.118741862475872</v>
       </c>
       <c r="K3" t="n">
-        <v>53.12527227401733</v>
+        <v>8.641024112701416</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1120050859451294</v>
+        <v>0.06796229839324951</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1889143180847168</v>
+        <v>0.09716684341430661</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2197840118408203</v>
+        <v>0.103192925453186</v>
       </c>
       <c r="O3" t="n">
-        <v>5.60025429725647</v>
+        <v>3.398114919662476</v>
       </c>
       <c r="P3" t="n">
-        <v>9.44571590423584</v>
+        <v>4.858342170715332</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.98920059204102</v>
+        <v>5.159646272659302</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-054431</t>
+          <t>20250730-090715</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>182.6363725662232</v>
+        <v>52.05677127838135</v>
       </c>
       <c r="D4" t="n">
-        <v>6.840000152587891</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4200952992189762</v>
+        <v>0.1377141363918781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.7647058963775635</v>
       </c>
       <c r="G4" t="n">
-        <v>0.756302535533905</v>
+        <v>0.640668511390686</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7547649145126343</v>
+        <v>0.5835371017456055</v>
       </c>
       <c r="I4" t="n">
-        <v>0.73758864402771</v>
+        <v>0.5859246850013733</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1505140662193298</v>
+        <v>0.1054959520697593</v>
       </c>
       <c r="K4" t="n">
-        <v>41.27623081207275</v>
+        <v>14.22434496879578</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1239917564392089</v>
+        <v>0.08350908756256099</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1887134790420532</v>
+        <v>0.0931906270980835</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1864602184295654</v>
+        <v>0.0910782623291015</v>
       </c>
       <c r="O4" t="n">
-        <v>6.199587821960449</v>
+        <v>4.175454378128052</v>
       </c>
       <c r="P4" t="n">
-        <v>9.435673952102659</v>
+        <v>4.659531354904175</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.323010921478271</v>
+        <v>4.553913116455078</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-054948</t>
+          <t>20250730-091016</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>190.9158828258514</v>
+        <v>92.5405695438385</v>
       </c>
       <c r="D5" t="n">
-        <v>6.010000228881836</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4007890034805644</v>
+        <v>0.139040518976465</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8101266026496887</v>
+        <v>0.7878788113594055</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7339003682136536</v>
+        <v>0.7369165420532227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6333333253860474</v>
+        <v>0.7051762938499451</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6181229948997498</v>
+        <v>0.707025408744812</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1744246333837509</v>
+        <v>0.104740485548973</v>
       </c>
       <c r="K5" t="n">
-        <v>43.23511672019959</v>
+        <v>13.85759663581848</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1197911310195922</v>
+        <v>0.0763823223114013</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1814025592803955</v>
+        <v>0.0960220861434936</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1860842418670654</v>
+        <v>0.0939629364013671</v>
       </c>
       <c r="O5" t="n">
-        <v>5.989556550979614</v>
+        <v>3.819116115570069</v>
       </c>
       <c r="P5" t="n">
-        <v>9.070127964019775</v>
+        <v>4.801104307174683</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.304212093353271</v>
+        <v>4.698146820068359</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-055450</t>
+          <t>20250730-091209</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C6" t="n">
-        <v>180.6105263233185</v>
+        <v>104.9686796665192</v>
       </c>
       <c r="D6" t="n">
-        <v>6.440000057220459</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4024757593870163</v>
+        <v>0.1379551570466223</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8533333539962769</v>
+        <v>0.8450704216957092</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7142857313156128</v>
+        <v>0.7098121047019958</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6871508359909058</v>
+        <v>0.7081272006034851</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6845070719718933</v>
+        <v>0.703125</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1520858407020568</v>
+        <v>0.110731229186058</v>
       </c>
       <c r="K6" t="n">
-        <v>40.78113889694214</v>
+        <v>13.89574933052063</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1110545682907104</v>
+        <v>0.0737368059158325</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1812065076828003</v>
+        <v>0.0955828285217285</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2035797643661499</v>
+        <v>0.0954281711578369</v>
       </c>
       <c r="O6" t="n">
-        <v>5.552728414535522</v>
+        <v>3.686840295791626</v>
       </c>
       <c r="P6" t="n">
-        <v>9.060325384140016</v>
+        <v>4.779141426086426</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.1789882183075</v>
+        <v>4.771408557891846</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-060001</t>
+          <t>20250730-091443</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>48.08496737480164</v>
+        <v>78.01521921157837</v>
       </c>
       <c r="D2" t="n">
-        <v>1.700000047683716</v>
+        <v>13.65999984741211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1323368312144765</v>
+        <v>0.255223516943091</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8674699068069458</v>
+        <v>0.9230769276618958</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7315855026245117</v>
+        <v>0.8320987820625305</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7349319458007812</v>
+        <v>0.838316023349762</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7326236963272095</v>
+        <v>0.8329238295555115</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0975943654775619</v>
+        <v>0.1039474010467529</v>
       </c>
       <c r="K2" t="n">
-        <v>15.58342695236206</v>
+        <v>29.26352453231812</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0871084356307983</v>
+        <v>0.0855157709121704</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1111379671096801</v>
+        <v>0.1742363500595092</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1167560768127441</v>
+        <v>0.1517188310623169</v>
       </c>
       <c r="O2" t="n">
-        <v>4.355421781539917</v>
+        <v>4.275788545608521</v>
       </c>
       <c r="P2" t="n">
-        <v>5.556898355484009</v>
+        <v>8.711817502975464</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.837803840637207</v>
+        <v>7.585941553115845</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-184751</t>
+          <t>20250731-015832</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>51.50541663169861</v>
+        <v>50.59505581855774</v>
       </c>
       <c r="D3" t="n">
-        <v>1.730000019073486</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1308030437816072</v>
+        <v>0.2527751792699862</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8799999952316284</v>
+        <v>0.8985507488250732</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7384230494499207</v>
+        <v>0.8289963006973267</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7524493932723999</v>
+        <v>0.8306148052215576</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7530468106269836</v>
+        <v>0.827369749546051</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09982419013977049</v>
+        <v>0.1140386313199997</v>
       </c>
       <c r="K3" t="n">
-        <v>15.60470747947693</v>
+        <v>29.96856093406677</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0804200410842895</v>
+        <v>0.097021689414978</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1100024271011352</v>
+        <v>0.1822340250015258</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1121698093414306</v>
+        <v>0.1443701410293579</v>
       </c>
       <c r="O3" t="n">
-        <v>4.021002054214478</v>
+        <v>4.851084470748901</v>
       </c>
       <c r="P3" t="n">
-        <v>5.500121355056763</v>
+        <v>9.111701250076294</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.608490467071533</v>
+        <v>7.218507051467895</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-184946</t>
+          <t>20250731-020123</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>38.95648241043091</v>
+        <v>59.2104480266571</v>
       </c>
       <c r="D4" t="n">
-        <v>1.679999947547913</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1362951537355398</v>
+        <v>0.2542608539489182</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7941176295280457</v>
+        <v>0.921052634716034</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.822857141494751</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6530612111091614</v>
+        <v>0.8147192001342773</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6946666836738586</v>
+        <v>0.8209718465805054</v>
       </c>
       <c r="J4" t="n">
-        <v>0.093399666249752</v>
+        <v>0.1202001497149467</v>
       </c>
       <c r="K4" t="n">
-        <v>9.927643537521362</v>
+        <v>29.18964886665344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0857620096206665</v>
+        <v>0.08024898052215571</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1137772178649902</v>
+        <v>0.1759844255447387</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1186304426193237</v>
+        <v>0.1425986194610595</v>
       </c>
       <c r="O4" t="n">
-        <v>4.288100481033325</v>
+        <v>4.012449026107788</v>
       </c>
       <c r="P4" t="n">
-        <v>5.688860893249512</v>
+        <v>8.799221277236938</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.931522130966187</v>
+        <v>7.129930973052979</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-185145</t>
+          <t>20250731-020347</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C5" t="n">
-        <v>87.7815990447998</v>
+        <v>110.5526316165924</v>
       </c>
       <c r="D5" t="n">
-        <v>1.690000057220459</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1301027108380134</v>
+        <v>0.2542513143480494</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9041095972061156</v>
+        <v>0.9090909361839294</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7898412942886353</v>
+        <v>0.7786458134651184</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7824451327323914</v>
+        <v>0.7718347907066345</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7764253616333008</v>
+        <v>0.780927836894989</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09714508056640619</v>
+        <v>0.1062950193881988</v>
       </c>
       <c r="K5" t="n">
-        <v>15.66137313842773</v>
+        <v>29.79242491722107</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08185315132141111</v>
+        <v>0.09622225284576411</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1083087110519409</v>
+        <v>0.1765423107147216</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1160664939880371</v>
+        <v>0.1448831510543823</v>
       </c>
       <c r="O5" t="n">
-        <v>4.092657566070557</v>
+        <v>4.811112642288208</v>
       </c>
       <c r="P5" t="n">
-        <v>5.415435552597046</v>
+        <v>8.827115535736084</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.803324699401856</v>
+        <v>7.244157552719116</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-185325</t>
+          <t>20250731-020618</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>74.17545199394226</v>
+        <v>63.75797700881958</v>
       </c>
       <c r="D6" t="n">
-        <v>1.710000038146973</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1301414351674574</v>
+        <v>0.2535167464188167</v>
       </c>
       <c r="F6" t="n">
-        <v>0.921052634716034</v>
+        <v>0.9189189076423644</v>
       </c>
       <c r="G6" t="n">
-        <v>0.793749988079071</v>
+        <v>0.8243992328643799</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7922329902648926</v>
+        <v>0.8076138496398926</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7966538071632385</v>
+        <v>0.8111035823822021</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09290127456188201</v>
+        <v>0.0920308753848075</v>
       </c>
       <c r="K6" t="n">
-        <v>15.53074288368225</v>
+        <v>24.34861707687378</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0797266721725463</v>
+        <v>0.06811940193176259</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0999887800216674</v>
+        <v>0.1792012500762939</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1141486549377441</v>
+        <v>0.1376437759399414</v>
       </c>
       <c r="O6" t="n">
-        <v>3.986333608627319</v>
+        <v>3.405970096588135</v>
       </c>
       <c r="P6" t="n">
-        <v>4.999439001083374</v>
+        <v>8.960062503814697</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.707432746887207</v>
+        <v>6.88218879699707</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-185600</t>
+          <t>20250731-020943</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>67.17160034179688</v>
+        <v>49.69220423698425</v>
       </c>
       <c r="D2" t="n">
-        <v>5.360000133514404</v>
+        <v>6.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.104162326303579</v>
+        <v>0.144377107421557</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6756756901741028</v>
+        <v>0.9066666960716248</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5908156037330627</v>
+        <v>0.7840405106544495</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4953820407390594</v>
+        <v>0.7832699418067932</v>
       </c>
       <c r="I2" t="n">
-        <v>0.496655523777008</v>
+        <v>0.7860317230224609</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1129870861768722</v>
+        <v>0.111276589334011</v>
       </c>
       <c r="K2" t="n">
-        <v>8.762815237045288</v>
+        <v>19.14726209640503</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0791342496871948</v>
+        <v>0.06345190048217771</v>
       </c>
       <c r="M2" t="n">
-        <v>0.092948317527771</v>
+        <v>0.1244076299667358</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0910789394378662</v>
+        <v>0.1255463933944702</v>
       </c>
       <c r="O2" t="n">
-        <v>3.956712484359741</v>
+        <v>3.172595024108887</v>
       </c>
       <c r="P2" t="n">
-        <v>4.64741587638855</v>
+        <v>6.220381498336792</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.553946971893311</v>
+        <v>6.277319669723511</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-083151</t>
+          <t>20250627-161301</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
-        <v>87.54258871078491</v>
+        <v>31.62995886802673</v>
       </c>
       <c r="D3" t="n">
-        <v>5.380000114440918</v>
+        <v>6.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1047634136261818</v>
+        <v>0.1449878141283988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8358209133148193</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7352328300476074</v>
+        <v>0.7586206793785095</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6507176756858826</v>
+        <v>0.7161383032798767</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6566217541694641</v>
+        <v>0.7181687951087952</v>
       </c>
       <c r="J3" t="n">
-        <v>0.103566825389862</v>
+        <v>0.1112867817282676</v>
       </c>
       <c r="K3" t="n">
-        <v>8.801921129226685</v>
+        <v>19.35022640228271</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0714699268341064</v>
+        <v>0.0563068914413452</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0963096046447753</v>
+        <v>0.1168089866638183</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0961419630050659</v>
+        <v>0.1200147533416748</v>
       </c>
       <c r="O3" t="n">
-        <v>3.573496341705322</v>
+        <v>2.815344572067261</v>
       </c>
       <c r="P3" t="n">
-        <v>4.81548023223877</v>
+        <v>5.840449333190918</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.807098150253296</v>
+        <v>6.00073766708374</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-083400</t>
+          <t>20250627-161505</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>125.8958480358124</v>
+        <v>58.61772918701172</v>
       </c>
       <c r="D4" t="n">
-        <v>5.380000114440918</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1047988848989469</v>
+        <v>0.1470048248302191</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7692307829856873</v>
+        <v>0.9142857193946838</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6986591219902039</v>
+        <v>0.7830065488815308</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6970127820968628</v>
+        <v>0.7368420958518982</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6951566934585571</v>
+        <v>0.7357811331748962</v>
       </c>
       <c r="J4" t="n">
-        <v>0.120906688272953</v>
+        <v>0.1075381636619567</v>
       </c>
       <c r="K4" t="n">
-        <v>8.521650552749634</v>
+        <v>19.63300824165344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07356871128082269</v>
+        <v>0.0698004245758056</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1080145168304443</v>
+        <v>0.1145829391479492</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1098702907562255</v>
+        <v>0.122821397781372</v>
       </c>
       <c r="O4" t="n">
-        <v>3.678435564041138</v>
+        <v>3.490021228790283</v>
       </c>
       <c r="P4" t="n">
-        <v>5.400725841522217</v>
+        <v>5.729146957397461</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.493514537811279</v>
+        <v>6.141069889068604</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-083630</t>
+          <t>20250627-161650</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>106.8194072246552</v>
+        <v>31.59505128860474</v>
       </c>
       <c r="D5" t="n">
-        <v>5.360000133514404</v>
+        <v>6.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1042187137806668</v>
+        <v>0.1449846388662562</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8732394576072693</v>
+        <v>0.8767123222351074</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7412587404251099</v>
+        <v>0.7618412375450134</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7372159361839294</v>
+        <v>0.7045454382896423</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7355666160583496</v>
+        <v>0.7080181837081909</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1232266798615455</v>
+        <v>0.1134355962276458</v>
       </c>
       <c r="K5" t="n">
-        <v>14.28191709518433</v>
+        <v>19.16315317153931</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0773811674118042</v>
+        <v>0.0587211656570434</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1004505395889282</v>
+        <v>0.1153432512283325</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09894622802734369</v>
+        <v>0.1324038314819336</v>
       </c>
       <c r="O5" t="n">
-        <v>3.86905837059021</v>
+        <v>2.936058282852173</v>
       </c>
       <c r="P5" t="n">
-        <v>5.022526979446411</v>
+        <v>5.767162561416626</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.947311401367188</v>
+        <v>6.62019157409668</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-083924</t>
+          <t>20250627-161903</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>92.7428572177887</v>
+        <v>45.83732128143311</v>
       </c>
       <c r="D6" t="n">
-        <v>5.360000133514404</v>
+        <v>6.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1042074950500612</v>
+        <v>0.1459119140493626</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7878788113594055</v>
+        <v>0.931506872177124</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6934673190116882</v>
+        <v>0.8071519732475281</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6727828979492188</v>
+        <v>0.8057366609573364</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6732824444770813</v>
+        <v>0.802890956401825</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1143030524253845</v>
+        <v>0.1165434867143631</v>
       </c>
       <c r="K6" t="n">
-        <v>8.892719268798828</v>
+        <v>19.15483283996582</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0762703847885131</v>
+        <v>0.0696837377548217</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0950699090957641</v>
+        <v>0.1237140655517578</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0964332628250122</v>
+        <v>0.1333547258377075</v>
       </c>
       <c r="O6" t="n">
-        <v>3.813519239425659</v>
+        <v>3.484186887741089</v>
       </c>
       <c r="P6" t="n">
-        <v>4.753495454788208</v>
+        <v>6.185703277587891</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.82166314125061</v>
+        <v>6.667736291885376</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-084213</t>
+          <t>20250627-162049</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9077,56 +9077,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>96.07636308670044</v>
+        <v>48.08496737480164</v>
       </c>
       <c r="D2" t="n">
-        <v>7.590000152587891</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1742823035234496</v>
+        <v>0.1323368312144765</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9473684430122375</v>
+        <v>0.8674699068069458</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8543689250946045</v>
+        <v>0.7315855026245117</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8481806516647339</v>
+        <v>0.7349319458007812</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8441064357757568</v>
+        <v>0.7326236963272095</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0998700261116027</v>
+        <v>0.0975943654775619</v>
       </c>
       <c r="K2" t="n">
-        <v>30.14391183853149</v>
+        <v>15.58342695236206</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0903130769729614</v>
+        <v>0.0871084356307983</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1747147703170776</v>
+        <v>0.1111379671096801</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1540854883193969</v>
+        <v>0.1167560768127441</v>
       </c>
       <c r="O2" t="n">
-        <v>4.515653848648071</v>
+        <v>4.355421781539917</v>
       </c>
       <c r="P2" t="n">
-        <v>8.735738515853882</v>
+        <v>5.556898355484009</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.704274415969849</v>
+        <v>5.837803840637207</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-103904</t>
+          <t>20250701-184751</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>47.58719158172608</v>
+        <v>51.50541663169861</v>
       </c>
       <c r="D3" t="n">
-        <v>7.480000019073486</v>
+        <v>1.730000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1731094618638356</v>
+        <v>0.1308030437816072</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9166666865348816</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8298906683921814</v>
+        <v>0.7384230494499207</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7913165092468262</v>
+        <v>0.7524493932723999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7952314019203186</v>
+        <v>0.7530468106269836</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0889933854341507</v>
+        <v>0.09982419013977049</v>
       </c>
       <c r="K3" t="n">
-        <v>30.17732810974121</v>
+        <v>15.60470747947693</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0950716209411621</v>
+        <v>0.0804200410842895</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1767632102966308</v>
+        <v>0.1100024271011352</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1410403633117675</v>
+        <v>0.1121698093414306</v>
       </c>
       <c r="O3" t="n">
-        <v>4.753581047058105</v>
+        <v>4.021002054214478</v>
       </c>
       <c r="P3" t="n">
-        <v>8.838160514831543</v>
+        <v>5.500121355056763</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.052018165588379</v>
+        <v>5.608490467071533</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-104215</t>
+          <t>20250701-184946</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>76.28964066505432</v>
+        <v>38.95648241043091</v>
       </c>
       <c r="D4" t="n">
-        <v>7.489999771118164</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1744789041113107</v>
+        <v>0.1362951537355398</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9142857193946838</v>
+        <v>0.7941176295280457</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7699877023696899</v>
+        <v>0.6666666865348816</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7620252966880798</v>
+        <v>0.6530612111091614</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7638888955116272</v>
+        <v>0.6946666836738586</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08722741901874539</v>
+        <v>0.093399666249752</v>
       </c>
       <c r="K4" t="n">
-        <v>30.48987889289856</v>
+        <v>9.927643537521362</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0848242044448852</v>
+        <v>0.0857620096206665</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1742941951751709</v>
+        <v>0.1137772178649902</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1502851009368896</v>
+        <v>0.1186304426193237</v>
       </c>
       <c r="O4" t="n">
-        <v>4.241210222244263</v>
+        <v>4.288100481033325</v>
       </c>
       <c r="P4" t="n">
-        <v>8.714709758758545</v>
+        <v>5.688860893249512</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.514255046844482</v>
+        <v>5.931522130966187</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-104437</t>
+          <t>20250701-185145</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="C5" t="n">
-        <v>65.04721522331238</v>
+        <v>87.7815990447998</v>
       </c>
       <c r="D5" t="n">
-        <v>7.519999980926514</v>
+        <v>1.690000057220459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.173105498154958</v>
+        <v>0.1301027108380134</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9473684430122375</v>
+        <v>0.9041095972061156</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8203821778297424</v>
+        <v>0.7898412942886353</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8167202472686768</v>
+        <v>0.7824451327323914</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8212927579879761</v>
+        <v>0.7764253616333008</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0949455201625824</v>
+        <v>0.09714508056640619</v>
       </c>
       <c r="K5" t="n">
-        <v>29.61674809455872</v>
+        <v>15.66137313842773</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0836220598220825</v>
+        <v>0.08185315132141111</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1732470750808716</v>
+        <v>0.1083087110519409</v>
       </c>
       <c r="N5" t="n">
-        <v>0.155406527519226</v>
+        <v>0.1160664939880371</v>
       </c>
       <c r="O5" t="n">
-        <v>4.181102991104126</v>
+        <v>4.092657566070557</v>
       </c>
       <c r="P5" t="n">
-        <v>8.662353754043579</v>
+        <v>5.415435552597046</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.770326375961304</v>
+        <v>5.803324699401856</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-104729</t>
+          <t>20250701-185325</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="C6" t="n">
-        <v>53.45933413505554</v>
+        <v>74.17545199394226</v>
       </c>
       <c r="D6" t="n">
-        <v>7.539999961853027</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1743572530421343</v>
+        <v>0.1301414351674574</v>
       </c>
       <c r="F6" t="n">
-        <v>0.931506872177124</v>
+        <v>0.921052634716034</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8167330622673035</v>
+        <v>0.793749988079071</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8229166865348816</v>
+        <v>0.7922329902648926</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8229098320007324</v>
+        <v>0.7966538071632385</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0839376747608184</v>
+        <v>0.09290127456188201</v>
       </c>
       <c r="K6" t="n">
-        <v>30.02488923072815</v>
+        <v>15.53074288368225</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0848014497756958</v>
+        <v>0.0797266721725463</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1844046783447265</v>
+        <v>0.0999887800216674</v>
       </c>
       <c r="N6" t="n">
-        <v>0.148233904838562</v>
+        <v>0.1141486549377441</v>
       </c>
       <c r="O6" t="n">
-        <v>4.24007248878479</v>
+        <v>3.986333608627319</v>
       </c>
       <c r="P6" t="n">
-        <v>9.220233917236328</v>
+        <v>4.999439001083374</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.411695241928101</v>
+        <v>5.707432746887207</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-104958</t>
+          <t>20250701-185600</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
